--- a/文档/传感器/语音控制模块/语音芯片sdk/CI13XX_SDK_ASR_ALG_V2.7.X/projects/offline_asr_alg_pro_sample/firmware/user_file/cmd_info/[60000]{cmd_info}.xlsx
+++ b/文档/传感器/语音控制模块/语音芯片sdk/CI13XX_SDK_ASR_ALG_V2.7.X/projects/offline_asr_alg_pro_sample/firmware/user_file/cmd_info/[60000]{cmd_info}.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -645,7 +645,7 @@
       <c r="B4" s="2" t="n"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>开风扇</t>
+          <t>打开风扇</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
@@ -653,11 +653,11 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0x3C81942</t>
+          <t>0x3C81941</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -684,11 +684,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>user_defined</t>
+          <t>random</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
         <v>3</v>
+      </c>
+      <c r="N4" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -730,7 +733,7 @@
         </is>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -738,7 +741,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -788,26 +791,26 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="2" t="n"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>防误</t>
+          <t>开风扇</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>43604</v>
+        <v>3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0xAA54</t>
+          <t>0x3C81942</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>200</v>
+        <v>97</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
@@ -830,34 +833,37 @@
         </is>
       </c>
       <c r="K7" s="2" t="n">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>user_defined</t>
+          <t>random</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>43604</v>
+        <v>3</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="2" t="n"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>&lt;welcome&gt;</t>
+          <t>关风扇</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>10001</v>
+        <v>5</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0x00</t>
+          <t>0x3C81982</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -880,11 +886,11 @@
         </is>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>user_defined</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
@@ -895,19 +901,19 @@
       <c r="B9" s="2" t="n"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>&lt;inactivate&gt;</t>
+          <t>防误</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>10002</v>
+        <v>43604</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0x00</t>
+          <t>0xAA54</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
@@ -930,26 +936,26 @@
         </is>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>user_defined</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>7</v>
+        <v>43604</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="2" t="n"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>&lt;beep&gt;</t>
+          <t>&lt;welcome&gt;</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>10003</v>
+        <v>10001</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -988,65 +994,165 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="2" t="n"/>
       <c r="C11" t="inlineStr">
         <is>
+          <t>&lt;inactivate&gt;</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>10002</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0x00</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>&lt;beep&gt;</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>10003</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0x00</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>&lt;baud_sync_req&gt;</t>
         </is>
       </c>
-      <c r="D11" s="2" t="n">
+      <c r="D13" s="2" t="n">
         <v>43605</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>0xAA55</t>
         </is>
       </c>
-      <c r="F11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="inlineStr">
+      <c r="F13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>random</t>
         </is>
       </c>
-      <c r="M11" s="2" t="n">
-        <v>9</v>
+      <c r="M13" s="2" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="G2 G3 G4 G5 G6 H2 H3 H4 H5 H6 I2 I3 I4 I5 I6 J2 J3 J4 J5 J6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="List Selection" prompt="Please select from the list" type="list">
+    <dataValidation sqref="G2 G3 G4 G5 G6 G7 G8 H2 H3 H4 H5 H6 H7 H8 I2 I3 I4 I5 I6 I7 I8 J2 J3 J4 J5 J6 J7 J8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="List Selection" prompt="Please select from the list" type="list">
       <formula1>"YES,NO"</formula1>
     </dataValidation>
-    <dataValidation sqref="L2 L3 L4 L5 L6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="List Selection" prompt="Please select from the list" type="list">
+    <dataValidation sqref="L2 L3 L4 L5 L6 L7 L8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="List Selection" prompt="Please select from the list" type="list">
       <formula1>"user_defined,random"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1060,7 +1166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1275,7 +1381,7 @@
       <c r="B4" s="2" t="n"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>开风扇</t>
+          <t>打开风扇</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
@@ -1283,11 +1389,11 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0x3C81942</t>
+          <t>0x3C81941</t>
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -1314,11 +1420,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>user_defined</t>
+          <t>random</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
         <v>3</v>
+      </c>
+      <c r="N4" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -1360,7 +1469,7 @@
         </is>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -1368,7 +1477,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -1418,26 +1527,26 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="2" t="n"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>防误</t>
+          <t>开风扇</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>43604</v>
+        <v>3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0xAA54</t>
+          <t>0x3C81942</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>200</v>
+        <v>97</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
@@ -1460,34 +1569,37 @@
         </is>
       </c>
       <c r="K7" s="2" t="n">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>user_defined</t>
+          <t>random</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>43604</v>
+        <v>3</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="2" t="n"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>&lt;welcome&gt;</t>
+          <t>关风扇</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>10001</v>
+        <v>5</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0x00</t>
+          <t>0x3C81982</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -1510,11 +1622,11 @@
         </is>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>user_defined</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
@@ -1525,19 +1637,19 @@
       <c r="B9" s="2" t="n"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>&lt;inactivate&gt;</t>
+          <t>防误</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>10002</v>
+        <v>43604</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0x00</t>
+          <t>0xAA54</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
@@ -1560,26 +1672,26 @@
         </is>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>user_defined</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>7</v>
+        <v>43604</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="2" t="n"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>&lt;beep&gt;</t>
+          <t>&lt;welcome&gt;</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>10003</v>
+        <v>10001</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1618,65 +1730,165 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="2" t="n"/>
       <c r="C11" t="inlineStr">
         <is>
+          <t>&lt;inactivate&gt;</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>10002</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0x00</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>&lt;beep&gt;</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>10003</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0x00</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>&lt;baud_sync_req&gt;</t>
         </is>
       </c>
-      <c r="D11" s="2" t="n">
+      <c r="D13" s="2" t="n">
         <v>43605</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>0xAA55</t>
         </is>
       </c>
-      <c r="F11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="inlineStr">
+      <c r="F13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>random</t>
         </is>
       </c>
-      <c r="M11" s="2" t="n">
-        <v>9</v>
+      <c r="M13" s="2" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="G2 G3 G4 G5 G6 H2 H3 H4 H5 H6 I2 I3 I4 I5 I6 J2 J3 J4 J5 J6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="List Selection" prompt="Please select from the list" type="list">
+    <dataValidation sqref="G2 G3 G4 G5 G6 G7 G8 H2 H3 H4 H5 H6 H7 H8 I2 I3 I4 I5 I6 I7 I8 J2 J3 J4 J5 J6 J7 J8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="List Selection" prompt="Please select from the list" type="list">
       <formula1>"YES,NO"</formula1>
     </dataValidation>
-    <dataValidation sqref="L2 L3 L4 L5 L6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="List Selection" prompt="Please select from the list" type="list">
+    <dataValidation sqref="L2 L3 L4 L5 L6 L7 L8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="List Selection" prompt="Please select from the list" type="list">
       <formula1>"user_defined,random"</formula1>
     </dataValidation>
   </dataValidations>

--- a/文档/传感器/语音控制模块/语音芯片sdk/CI13XX_SDK_ASR_ALG_V2.7.X/projects/offline_asr_alg_pro_sample/firmware/user_file/cmd_info/[60000]{cmd_info}.xlsx
+++ b/文档/传感器/语音控制模块/语音芯片sdk/CI13XX_SDK_ASR_ALG_V2.7.X/projects/offline_asr_alg_pro_sample/firmware/user_file/cmd_info/[60000]{cmd_info}.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -901,19 +901,19 @@
       <c r="B9" s="2" t="n"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>防误</t>
+          <t>开空调</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>43604</v>
+        <v>10</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0xAA54</t>
+          <t>0x3C81941</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>200</v>
+        <v>97</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="K9" s="2" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -944,26 +944,26 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>43604</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="2" t="n"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>&lt;welcome&gt;</t>
+          <t>关空调</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>10001</v>
+        <v>11</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0x00</t>
+          <t>0x3C81984</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
@@ -990,30 +990,30 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>user_defined</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="2" t="n"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>&lt;inactivate&gt;</t>
+          <t>开抽湿机</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>10002</v>
+        <v>12</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0x00</t>
+          <t>0x000C</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
@@ -1040,30 +1040,30 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>user_defined</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="2" t="n"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>&lt;beep&gt;</t>
+          <t>关抽湿机</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>10003</v>
+        <v>13</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0x00</t>
+          <t>0x000D</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
@@ -1090,69 +1090,269 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>user_defined</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="2" t="n"/>
       <c r="C13" t="inlineStr">
         <is>
+          <t>防误</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>43604</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0xAA54</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>user_defined</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>43604</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>&lt;welcome&gt;</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>10001</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0x00</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>&lt;inactivate&gt;</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>10002</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0x00</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>&lt;beep&gt;</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>10003</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0x00</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" t="inlineStr">
+        <is>
           <t>&lt;baud_sync_req&gt;</t>
         </is>
       </c>
-      <c r="D13" s="2" t="n">
+      <c r="D17" s="2" t="n">
         <v>43605</v>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>0xAA55</t>
         </is>
       </c>
-      <c r="F13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="inlineStr">
+      <c r="F17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t>random</t>
         </is>
       </c>
-      <c r="M13" s="2" t="n">
-        <v>10</v>
+      <c r="M17" s="2" t="n">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="G2 G3 G4 G5 G6 G7 G8 H2 H3 H4 H5 H6 H7 H8 I2 I3 I4 I5 I6 I7 I8 J2 J3 J4 J5 J6 J7 J8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="List Selection" prompt="Please select from the list" type="list">
+    <dataValidation sqref="G2 G3 G4 G5 G6 G7 G8 G9 G10 G11 G12 H2 H3 H4 H5 H6 H7 H8 H9 H10 H11 H12 I2 I3 I4 I5 I6 I7 I8 I9 I10 I11 I12 J2 J3 J4 J5 J6 J7 J8 J9 J10 J11 J12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="List Selection" prompt="Please select from the list" type="list">
       <formula1>"YES,NO"</formula1>
     </dataValidation>
-    <dataValidation sqref="L2 L3 L4 L5 L6 L7 L8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="List Selection" prompt="Please select from the list" type="list">
+    <dataValidation sqref="L2 L3 L4 L5 L6 L7 L8 L9 L10 L11 L12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="List Selection" prompt="Please select from the list" type="list">
       <formula1>"user_defined,random"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1166,7 +1366,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1637,19 +1837,19 @@
       <c r="B9" s="2" t="n"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>防误</t>
+          <t>开空调</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>43604</v>
+        <v>10</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0xAA54</t>
+          <t>0x3C81941</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>200</v>
+        <v>97</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
@@ -1672,7 +1872,7 @@
         </is>
       </c>
       <c r="K9" s="2" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -1680,26 +1880,26 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>43604</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="2" t="n"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>&lt;welcome&gt;</t>
+          <t>关空调</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>10001</v>
+        <v>11</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0x00</t>
+          <t>0x3C81984</t>
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
@@ -1726,30 +1926,30 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>user_defined</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="2" t="n"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>&lt;inactivate&gt;</t>
+          <t>开抽湿机</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>10002</v>
+        <v>12</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0x00</t>
+          <t>0x000C</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
@@ -1776,30 +1976,30 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>user_defined</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="2" t="n"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>&lt;beep&gt;</t>
+          <t>关抽湿机</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>10003</v>
+        <v>13</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0x00</t>
+          <t>0x000D</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
@@ -1826,69 +2026,269 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>random</t>
+          <t>user_defined</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="2" t="n"/>
       <c r="C13" t="inlineStr">
         <is>
+          <t>防误</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>43604</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0xAA54</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>user_defined</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>43604</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>&lt;welcome&gt;</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>10001</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0x00</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>&lt;inactivate&gt;</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>10002</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0x00</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>&lt;beep&gt;</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>10003</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0x00</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>random</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" t="inlineStr">
+        <is>
           <t>&lt;baud_sync_req&gt;</t>
         </is>
       </c>
-      <c r="D13" s="2" t="n">
+      <c r="D17" s="2" t="n">
         <v>43605</v>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>0xAA55</t>
         </is>
       </c>
-      <c r="F13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="inlineStr">
+      <c r="F17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t>random</t>
         </is>
       </c>
-      <c r="M13" s="2" t="n">
-        <v>10</v>
+      <c r="M17" s="2" t="n">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="G2 G3 G4 G5 G6 G7 G8 H2 H3 H4 H5 H6 H7 H8 I2 I3 I4 I5 I6 I7 I8 J2 J3 J4 J5 J6 J7 J8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="List Selection" prompt="Please select from the list" type="list">
+    <dataValidation sqref="G2 G3 G4 G5 G6 G7 G8 G9 G10 G11 G12 H2 H3 H4 H5 H6 H7 H8 H9 H10 H11 H12 I2 I3 I4 I5 I6 I7 I8 I9 I10 I11 I12 J2 J3 J4 J5 J6 J7 J8 J9 J10 J11 J12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="List Selection" prompt="Please select from the list" type="list">
       <formula1>"YES,NO"</formula1>
     </dataValidation>
-    <dataValidation sqref="L2 L3 L4 L5 L6 L7 L8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="List Selection" prompt="Please select from the list" type="list">
+    <dataValidation sqref="L2 L3 L4 L5 L6 L7 L8 L9 L10 L11 L12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="List Selection" prompt="Please select from the list" type="list">
       <formula1>"user_defined,random"</formula1>
     </dataValidation>
   </dataValidations>
